--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484304_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484304_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.677</v>
+        <v>4.274</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4834</v>
+        <v>7.3528</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8064</v>
+        <v>-3.0788</v>
       </c>
       <c r="G2" t="n">
         <v>3.2596</v>
@@ -610,13 +610,13 @@
         <v>3.1255</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4458</v>
+        <v>0.1513</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8941</v>
+        <v>-0.0246</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4483</v>
+        <v>0.1759</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2856</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6354</v>
+        <v>2.262</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1993</v>
+        <v>2.8259</v>
       </c>
       <c r="F3" t="n">
         <v>-0.5638</v>
@@ -688,10 +688,10 @@
         <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8089</v>
+        <v>-0.1823</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8335</v>
+        <v>-0.2069</v>
       </c>
       <c r="U3" t="n">
         <v>0.0246</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9407</v>
+        <v>2.0765</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9527</v>
+        <v>1.6111</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0121</v>
+        <v>0.4655</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3389</v>
+        <v>-2.8594</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3883</v>
+        <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7272</v>
+        <v>-2.9402</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6433</v>
+        <v>0.4024</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4814</v>
+        <v>1.7229</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1619</v>
+        <v>-1.3206</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9822</v>
+        <v>-3.2617</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0931</v>
+        <v>-1.6421</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8891</v>
+        <v>-1.6196</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7581</v>
+        <v>3.7115</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1488</v>
+        <v>3.7115</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0376</v>
+        <v>1.5016</v>
       </c>
       <c r="T4" t="n">
-        <v>2.779</v>
+        <v>1.2087</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2586</v>
+        <v>0.2929</v>
       </c>
       <c r="V4" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.4373</v>
-      </c>
       <c r="X4" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.707</v>
+        <v>1.1793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3777</v>
+        <v>0.6294</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3293</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8594</v>
+        <v>-0.4461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0808</v>
+        <v>0.1878</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9402</v>
+        <v>-0.6338</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4024</v>
+        <v>0.1031</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7229</v>
+        <v>0.7368</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3206</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2617</v>
+        <v>-0.5492</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6421</v>
+        <v>-0.549</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6196</v>
+        <v>-0.0002</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7115</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7115</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1321</v>
+        <v>0.6486</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0246</v>
+        <v>0.5262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1567</v>
+        <v>0.1224</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4382</v>
+        <v>0.4204</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.139</v>
+        <v>1.0324</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5772</v>
+        <v>-0.612</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4461</v>
+        <v>-0.2025</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1878</v>
+        <v>-0.9714</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6338</v>
+        <v>0.7688</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1031</v>
+        <v>2.529</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7368</v>
+        <v>0.6804</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.8486</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5492</v>
+        <v>-2.7316</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.549</v>
+        <v>-1.6518</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0002</v>
+        <v>-1.0797</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0925</v>
+        <v>0.8034</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2421</v>
+        <v>0.8242</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1496</v>
+        <v>-0.0208</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2102</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.64</v>
+        <v>-0.6827</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0028</v>
+        <v>2.1932</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3628</v>
+        <v>-2.8759</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.0154</v>
+        <v>-0.3389</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7813</v>
+        <v>1.3883</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.2341</v>
+        <v>-1.7272</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.7769</v>
+        <v>2.6433</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1867</v>
+        <v>2.4814</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.9637</v>
+        <v>0.1619</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2384</v>
+        <v>-2.9822</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.968</v>
+        <v>-1.0931</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2704</v>
+        <v>-1.8891</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2748</v>
+        <v>1.4143</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2865</v>
+        <v>1.0195</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0117</v>
+        <v>0.3948</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3191</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.441</v>
+        <v>2.4373</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1219</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1495</v>
+        <v>-1.2407</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5648</v>
+        <v>-2.549</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5847</v>
+        <v>1.3083</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2025</v>
+        <v>-5.0154</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9714</v>
+        <v>-0.7813</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7688</v>
+        <v>-4.2341</v>
       </c>
       <c r="J8" t="n">
-        <v>2.529</v>
+        <v>-3.7769</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6804</v>
+        <v>0.1867</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8486</v>
+        <v>-3.9637</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7316</v>
+        <v>-1.2384</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6518</v>
+        <v>-0.968</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0797</v>
+        <v>-0.2704</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>2.7348</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7665999999999999</v>
+        <v>1.6742</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.773</v>
+        <v>1.7403</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0065</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2102</v>
+        <v>1.3191</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>1.441</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3991</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8154</v>
+        <v>-2.7115</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3882</v>
+        <v>-1.3388</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4272</v>
+        <v>-1.3727</v>
       </c>
       <c r="G9" t="n">
         <v>-2.964</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6212</v>
+        <v>0.725</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8545</v>
+        <v>0.9039</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0417</v>
+        <v>-2.8861</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6871</v>
+        <v>-2.586</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3546</v>
+        <v>-0.3001</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2342</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2801</v>
+        <v>-0.1245</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0467</v>
+        <v>0.0544</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V10" t="n">
         <v>0.2772</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0459</v>
+        <v>-5.0777</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.481</v>
+        <v>-5.5129</v>
       </c>
       <c r="F11" t="n">
         <v>0.4351</v>
@@ -1312,10 +1312,10 @@
         <v>3.5162</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4172</v>
+        <v>2.3854</v>
       </c>
       <c r="T11" t="n">
-        <v>3.09</v>
+        <v>2.0582</v>
       </c>
       <c r="U11" t="n">
         <v>0.3272</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.294199999999999</v>
+        <v>-2.386500000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>2.750200000000002</v>
+        <v>3.658099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.0444</v>
+        <v>-6.0445</v>
       </c>
       <c r="G12" t="n">
         <v>-15.4355</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9718</v>
+        <v>-3.971799999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-11.4638</v>
@@ -1390,22 +1390,22 @@
         <v>23.4413</v>
       </c>
       <c r="S12" t="n">
-        <v>8.089</v>
+        <v>8.996999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>7.196</v>
+        <v>8.103899999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8932</v>
+        <v>0.893</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8316999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>8.4206</v>
+        <v>8.420599999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.252400000000002</v>
+        <v>-9.2524</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3794</v>
+        <v>6.3807</v>
       </c>
       <c r="E13" t="n">
-        <v>6.353</v>
+        <v>5.9485</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0264</v>
+        <v>0.4322</v>
       </c>
       <c r="G13" t="n">
         <v>6.2317</v>
@@ -1468,13 +1468,13 @@
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4815</v>
+        <v>-0.4801</v>
       </c>
       <c r="T13" t="n">
-        <v>0.311</v>
+        <v>-0.0935</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7924</v>
+        <v>-0.3866</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5429</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2066</v>
+        <v>4.1102</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9277</v>
+        <v>5.5344</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7211</v>
+        <v>-1.4242</v>
       </c>
       <c r="G14" t="n">
         <v>3.368</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8088</v>
+        <v>-0.9052</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8941</v>
+        <v>-0.2874</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9147</v>
+        <v>-0.6179</v>
       </c>
       <c r="V14" t="n">
         <v>2.0382</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1976</v>
+        <v>3.2373</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0279</v>
+        <v>0.5788</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2255</v>
+        <v>2.6586</v>
       </c>
       <c r="G15" t="n">
         <v>5.5125</v>
@@ -1624,13 +1624,13 @@
         <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.6067</v>
+        <v>-1.5669</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0756</v>
+        <v>-0.4689</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.531</v>
+        <v>-1.098</v>
       </c>
       <c r="V15" t="n">
         <v>3.0033</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9191</v>
+        <v>0.7778</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5726</v>
+        <v>2.2692</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6534</v>
+        <v>-1.4914</v>
       </c>
       <c r="G16" t="n">
         <v>1.8835</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1209</v>
+        <v>-1.2622</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5201</v>
+        <v>0.2167</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.641</v>
+        <v>-1.479</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8201000000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0074</v>
+        <v>-0.1332</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4994</v>
+        <v>-0.0352</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.492</v>
+        <v>-0.098</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3193</v>
+        <v>0.0835</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8138</v>
+        <v>0.515</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.133</v>
+        <v>-0.4315</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0441</v>
+        <v>0.2531</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6373</v>
+        <v>0.8186</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5655</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3634</v>
+        <v>-0.1696</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8235</v>
+        <v>-0.3036</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5399</v>
+        <v>0.134</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2532</v>
+        <v>-0.9981</v>
       </c>
       <c r="T17" t="n">
-        <v>0.432</v>
+        <v>-0.5302</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1789</v>
+        <v>-0.4679</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2446</v>
+        <v>-0.1598</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3385</v>
+        <v>0.196</v>
       </c>
       <c r="F18" t="n">
-        <v>0.094</v>
+        <v>-0.3558</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0835</v>
+        <v>-0.3193</v>
       </c>
       <c r="H18" t="n">
-        <v>0.515</v>
+        <v>0.8138</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4315</v>
+        <v>-1.133</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2531</v>
+        <v>1.0441</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8186</v>
+        <v>1.6373</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5655</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1696</v>
+        <v>-1.3634</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3036</v>
+        <v>-0.8235</v>
       </c>
       <c r="O18" t="n">
-        <v>0.134</v>
+        <v>-0.5399</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1094</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8335</v>
+        <v>0.1287</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2759</v>
+        <v>-0.0427</v>
       </c>
       <c r="V18" t="n">
+        <v>-0.1219</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.2186</v>
-      </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.598</v>
+        <v>-0.4696</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8544</v>
+        <v>-0.7533</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2564</v>
+        <v>0.2837</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2175</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2515</v>
+        <v>-0.1231</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2515</v>
+        <v>-0.2242</v>
       </c>
       <c r="V19" t="n">
         <v>0.0664</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.944</v>
+        <v>-1.5447</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8123</v>
+        <v>-1.7112</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1317</v>
+        <v>0.1665</v>
       </c>
       <c r="G20" t="n">
         <v>1.2351</v>
@@ -2014,13 +2014,13 @@
         <v>3.1255</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1236</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2062</v>
+        <v>-0.1051</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9174</v>
+        <v>-0.6192</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2741</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7407</v>
+        <v>-3.1271</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0502</v>
+        <v>-2.3535</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6905</v>
+        <v>-0.7736</v>
       </c>
       <c r="G21" t="n">
         <v>-1.024</v>
@@ -2092,13 +2092,13 @@
         <v>3.1255</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5167</v>
+        <v>-0.9031</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2863</v>
+        <v>-0.017</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8031</v>
+        <v>-0.8861</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3953</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8885</v>
+        <v>-4.4291</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2248</v>
+        <v>-3.6293</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6637</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-1.318</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6768</v>
+        <v>0.1362</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5668</v>
+        <v>0.1624</v>
       </c>
       <c r="U22" t="n">
-        <v>0.11</v>
+        <v>-0.0262</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.2943</v>
+        <v>4.6425</v>
       </c>
       <c r="E23" t="n">
-        <v>6.044599999999999</v>
+        <v>6.0444</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7501</v>
+        <v>-1.4019</v>
       </c>
       <c r="G23" t="n">
         <v>15.4355</v>
@@ -2248,13 +2248,13 @@
         <v>18.5578</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.089099999999998</v>
+        <v>-6.7408</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8931999999999998</v>
+        <v>-0.8931999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.195899999999998</v>
+        <v>-5.8478</v>
       </c>
       <c r="V23" t="n">
         <v>0.8316999999999996</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484304_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484304_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-3.1136</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>-0.3991</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6827</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1932</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8759</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3389</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3883</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7272</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6433</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4814</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9822</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0931</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8891</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4143</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0195</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3948</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2407</v>
+        <v>-0.6827</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.549</v>
+        <v>2.1932</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3083</v>
+        <v>-2.8759</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.0154</v>
+        <v>-0.3389</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7813</v>
+        <v>1.3883</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.2341</v>
+        <v>-1.7272</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.7769</v>
+        <v>2.6433</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1867</v>
+        <v>2.4814</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.9637</v>
+        <v>0.1619</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2384</v>
+        <v>-2.9822</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.968</v>
+        <v>-1.0931</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2704</v>
+        <v>-1.8891</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6742</v>
+        <v>1.4143</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7403</v>
+        <v>1.0195</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.3948</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3191</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.441</v>
+        <v>2.4373</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1219</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7115</v>
+        <v>-1.2407</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3388</v>
+        <v>-2.549</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3727</v>
+        <v>1.3083</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.964</v>
+        <v>-5.0154</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2354</v>
+        <v>-0.7813</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7286</v>
+        <v>-4.2341</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.266</v>
+        <v>-3.7769</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3469</v>
+        <v>0.1867</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>-3.9637</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.698</v>
+        <v>-1.2384</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8885</v>
+        <v>-0.968</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8095</v>
+        <v>-0.2704</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>0.725</v>
+        <v>1.6742</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9039</v>
+        <v>1.7403</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1789</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>1.3191</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8861</v>
+        <v>-2.7115</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.586</v>
+        <v>-1.3388</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3001</v>
+        <v>-1.3727</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2342</v>
+        <v>-2.964</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6565</v>
+        <v>-2.2354</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5778</v>
+        <v>-0.7286</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9409</v>
+        <v>-1.266</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6332</v>
+        <v>-1.3469</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3077</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2933</v>
+        <v>-1.698</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0233</v>
+        <v>-0.8885</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.27</v>
+        <v>-0.8095</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1245</v>
+        <v>0.725</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0544</v>
+        <v>0.9039</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1789</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2772</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0777</v>
+        <v>-2.8861</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5129</v>
+        <v>-2.586</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4351</v>
+        <v>-0.3001</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.466</v>
+        <v>-3.2342</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3372</v>
+        <v>-1.6565</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8032</v>
+        <v>-1.5778</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3434</v>
+        <v>-1.9409</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7843</v>
+        <v>-0.6332</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1277</v>
+        <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1226</v>
+        <v>-1.2933</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4472</v>
+        <v>-1.0233</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6755</v>
+        <v>-0.27</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.3208</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.837</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5162</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3854</v>
+        <v>-0.1245</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0582</v>
+        <v>0.0544</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3272</v>
+        <v>-0.1789</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6763</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2856</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.386500000000002</v>
+        <v>-5.3847</v>
       </c>
       <c r="E12" t="n">
-        <v>3.658099999999999</v>
+        <v>-5.8198</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.0445</v>
+        <v>0.4351</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.4355</v>
+        <v>-3.773</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.971799999999999</v>
+        <v>0.0302</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.4638</v>
+        <v>-3.8032</v>
       </c>
       <c r="J12" t="n">
-        <v>5.691000000000001</v>
+        <v>-1.6504</v>
       </c>
       <c r="K12" t="n">
-        <v>8.3803</v>
+        <v>1.4773</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6894</v>
+        <v>-3.1277</v>
       </c>
       <c r="M12" t="n">
-        <v>-21.1264</v>
+        <v>-2.1226</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.3523</v>
+        <v>-1.4472</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.774099999999999</v>
+        <v>-0.6755</v>
       </c>
       <c r="P12" t="n">
-        <v>4.883599999999999</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.5575</v>
+        <v>-6.837</v>
       </c>
       <c r="R12" t="n">
-        <v>23.4413</v>
+        <v>3.5162</v>
       </c>
       <c r="S12" t="n">
-        <v>8.996999999999998</v>
+        <v>2.3854</v>
       </c>
       <c r="T12" t="n">
-        <v>8.103899999999999</v>
+        <v>2.0582</v>
       </c>
       <c r="U12" t="n">
-        <v>0.893</v>
+        <v>0.3272</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8316999999999999</v>
+        <v>-0.6763</v>
       </c>
       <c r="W12" t="n">
-        <v>8.420599999999999</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.2524</v>
+        <v>-1.2856</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3807</v>
+        <v>-2.386500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9485</v>
+        <v>3.6582</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4322</v>
+        <v>-6.0445</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2317</v>
+        <v>-15.4355</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0758</v>
+        <v>-3.9718</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1559</v>
+        <v>-11.4638</v>
       </c>
       <c r="J13" t="n">
-        <v>6.042</v>
+        <v>5.691000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8857</v>
+        <v>8.3803</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1563</v>
+        <v>-2.6894</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1897</v>
+        <v>-21.1264</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1901</v>
+        <v>-12.3523</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0004</v>
+        <v>-8.774099999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-18.5575</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1721</v>
+        <v>23.44130000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4801</v>
+        <v>8.996999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0935</v>
+        <v>8.103900000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3866</v>
+        <v>0.8929999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5429</v>
+        <v>-0.8317</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>8.4206</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5429</v>
-      </c>
+        <v>-9.2524</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1102</v>
+        <v>6.3807</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5344</v>
+        <v>5.9485</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4242</v>
+        <v>0.4322</v>
       </c>
       <c r="G14" t="n">
-        <v>3.368</v>
+        <v>6.2317</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4252</v>
+        <v>3.0758</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9428</v>
+        <v>3.1559</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8774</v>
+        <v>6.042</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0683</v>
+        <v>2.8857</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8091</v>
+        <v>3.1563</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5095</v>
+        <v>0.1897</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6431</v>
+        <v>0.1901</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1336</v>
+        <v>-0.0004</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9052</v>
+        <v>-0.4801</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2874</v>
+        <v>-0.0935</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6179</v>
+        <v>-0.3866</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0382</v>
+        <v>-0.5429</v>
       </c>
       <c r="W14" t="n">
-        <v>4.8745</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8364</v>
+        <v>-0.5429</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2373</v>
+        <v>4.1102</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5788</v>
+        <v>5.5344</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6586</v>
+        <v>-1.4242</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5125</v>
+        <v>3.368</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3009</v>
+        <v>1.4252</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2116</v>
+        <v>1.9428</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9479</v>
+        <v>3.8774</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2185</v>
+        <v>2.0683</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7294</v>
+        <v>1.8091</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5646</v>
+        <v>-0.5095</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9176</v>
+        <v>-0.6431</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4822</v>
+        <v>0.1336</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.7115</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.837</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5669</v>
+        <v>-0.9052</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4689</v>
+        <v>-0.2874</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.098</v>
+        <v>-0.6179</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0033</v>
+        <v>2.0382</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9369</v>
+        <v>4.8745</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0664</v>
+        <v>-2.8364</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7778</v>
+        <v>3.2373</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2692</v>
+        <v>0.5788</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4914</v>
+        <v>2.6586</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8835</v>
+        <v>5.5125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2382</v>
+        <v>3.3009</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6453</v>
+        <v>2.2116</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0525</v>
+        <v>4.9479</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3507</v>
+        <v>4.2185</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7017</v>
+        <v>0.7294</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.169</v>
+        <v>0.5646</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1125</v>
+        <v>-0.9176</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9435</v>
+        <v>1.4822</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-6.837</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>3.1255</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2622</v>
+        <v>-1.5669</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2167</v>
+        <v>-0.4689</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.479</v>
+        <v>-1.098</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8201000000000001</v>
+        <v>3.0033</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.9369</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8201000000000001</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1332</v>
+        <v>0.7778</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0352</v>
+        <v>2.2692</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.098</v>
+        <v>-1.4914</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0835</v>
+        <v>1.8835</v>
       </c>
       <c r="H17" t="n">
-        <v>0.515</v>
+        <v>0.2382</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4315</v>
+        <v>1.6453</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2531</v>
+        <v>2.0525</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8186</v>
+        <v>1.3507</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5655</v>
+        <v>0.7017</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1696</v>
+        <v>-0.169</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3036</v>
+        <v>-1.1125</v>
       </c>
       <c r="O17" t="n">
-        <v>0.134</v>
+        <v>0.9435</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9981</v>
+        <v>-1.2622</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5302</v>
+        <v>0.2167</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4679</v>
+        <v>-1.479</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.8201000000000001</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1598</v>
+        <v>-0.1332</v>
       </c>
       <c r="E18" t="n">
-        <v>0.196</v>
+        <v>-0.0352</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3558</v>
+        <v>-0.098</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3193</v>
+        <v>0.0835</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8138</v>
+        <v>0.515</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.133</v>
+        <v>-0.4315</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0441</v>
+        <v>0.2531</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6373</v>
+        <v>0.8186</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5655</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3634</v>
+        <v>-0.1696</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8235</v>
+        <v>-0.3036</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5399</v>
+        <v>0.134</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.9981</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1287</v>
+        <v>-0.5302</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0427</v>
+        <v>-0.4679</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4696</v>
+        <v>-0.1598</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7533</v>
+        <v>0.196</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2837</v>
+        <v>-0.3558</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2175</v>
+        <v>-0.3193</v>
       </c>
       <c r="H19" t="n">
-        <v>0.012</v>
+        <v>0.8138</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2296</v>
+        <v>-1.133</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1223</v>
+        <v>1.0441</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0819</v>
+        <v>1.6373</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3399</v>
+        <v>-1.3634</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0698</v>
+        <v>-0.8235</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.27</v>
+        <v>-0.5399</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1231</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1011</v>
+        <v>0.1287</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2242</v>
+        <v>-0.0427</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0664</v>
+        <v>-0.1219</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0664</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5447</v>
+        <v>-0.4696</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7112</v>
+        <v>-0.7533</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1665</v>
+        <v>0.2837</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2351</v>
+        <v>-0.2175</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8549</v>
+        <v>0.012</v>
       </c>
       <c r="I20" t="n">
-        <v>2.09</v>
+        <v>-0.2296</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0235</v>
+        <v>0.1223</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1461</v>
+        <v>0.0819</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8774</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7884</v>
+        <v>-0.3399</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.001</v>
+        <v>-0.0698</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2126</v>
+        <v>-0.27</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1255</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.1231</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1051</v>
+        <v>0.1011</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6192</v>
+        <v>-0.2242</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2741</v>
+        <v>0.0664</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5513</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1271</v>
+        <v>-1.5447</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3535</v>
+        <v>-1.7112</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7736</v>
+        <v>0.1665</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.024</v>
+        <v>1.2351</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.142</v>
+        <v>-0.8549</v>
       </c>
       <c r="I21" t="n">
-        <v>2.118</v>
+        <v>2.09</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6485</v>
+        <v>2.0235</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2011</v>
+        <v>1.1461</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8496</v>
+        <v>0.8774</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6724</v>
+        <v>-0.7884</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9409</v>
+        <v>-2.001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2685</v>
+        <v>1.2126</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R21" t="n">
         <v>3.1255</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9031</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.017</v>
+        <v>-0.1051</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8861</v>
+        <v>-0.6192</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3953</v>
+        <v>-1.2741</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3405</v>
+        <v>-1.5513</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4291</v>
+        <v>-3.1271</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6293</v>
+        <v>-2.3535</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.7736</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.318</v>
+        <v>-1.024</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4121</v>
+        <v>-3.142</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09420000000000001</v>
+        <v>2.118</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1152</v>
+        <v>0.6485</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6536</v>
+        <v>-1.2011</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7688</v>
+        <v>1.8496</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4332</v>
+        <v>-1.6724</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7585</v>
+        <v>-1.9409</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>0.2685</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1255</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>3.1255</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1362</v>
+        <v>-0.9031</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1624</v>
+        <v>-0.017</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0262</v>
+        <v>-0.8861</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1219</v>
+        <v>-1.3953</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-4.4291</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.6293</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.7999000000000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.318</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.4121</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.6536</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.7688</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.4332</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.7585</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.1219</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.1219</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484304_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>4.6425</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>6.0444</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-1.4019</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>15.4355</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>3.971900000000001</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>11.4637</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>21.1265</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>12.3524</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>8.774100000000001</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-5.6911</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-8.3804</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>2.6894</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>-4.8836</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-23.4411</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>18.5578</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>-6.7408</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>-0.8931999999999999</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>-5.8478</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>0.8316999999999996</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>9.252300000000002</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-8.4208</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
